--- a/greggs-dcf.xlsx
+++ b/greggs-dcf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fd0138832153f364/Documents/Finance portfolio projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1440" documentId="8_{E574A8F5-FCA4-47C3-805C-C8A3CDB2F26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA74E56A-EE93-44D6-94C7-D08E45EBC29B}"/>
+  <xr:revisionPtr revIDLastSave="1484" documentId="8_{E574A8F5-FCA4-47C3-805C-C8A3CDB2F26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51F13127-8C77-4A6A-AB27-D93B031F2829}"/>
   <bookViews>
     <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" firstSheet="2" activeTab="3" xr2:uid="{0C3DFFD8-A44E-4D0C-AF64-63871CDFD5C9}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="99">
   <si>
     <t>Greggs DCF - Historicals</t>
   </si>
@@ -336,103 +336,31 @@
     <t>Share price - today's live price (LSE: GRG), converted from pence to £. Only today's price is needed.</t>
   </si>
   <si>
-    <t xml:space="preserve">Tab 2 - DCF model </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purpose: turns the historicals into a valuation, in 4 stages - assumptions, forecast, discounting and the valuation bridge, plus a WACC build </t>
-  </si>
-  <si>
-    <t>Assumptions:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue growth 8%: below the recent 11% as growth slows but the estate keeps expanding </t>
-  </si>
-  <si>
-    <t xml:space="preserve">EBIT margin 9.8%: three year average; margins have been stable </t>
-  </si>
-  <si>
-    <t>Tax 25%: UK statutory corporation tax rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D&amp;A 7% of revenue: steady recent ratio </t>
-  </si>
-  <si>
-    <t>Capex 11.5% of revnue: revent two year average</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working capital 0.25% of revenue: Greggs takes cash at the till </t>
-  </si>
-  <si>
-    <t>WACC 10.69%: built from CAPM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminal growth 2% - near long run UK GDP/inflation </t>
-  </si>
-  <si>
-    <t>WACC build</t>
-  </si>
-  <si>
-    <t>Cost of equity = risk-free (4.94%) + beta (1.15) × ERP (5%) = ~10.7% (CAPM</t>
-  </si>
-  <si>
-    <t>(CAPM)</t>
-  </si>
-  <si>
-    <t>Cost of debt ~3% after tax — immaterial, as Greggs has almost no debt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab 3 - sensitivity </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purpose: Shows the valuation is a range, not a false precise single figure. A grid varying WACC (down) agaisnt terminal growth (across), with value per share in each cell. </t>
-  </si>
-  <si>
-    <t>Built with Excel's Data Table (What If Analysis). Row input = terminal growth; column input = WACC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCF = discounted </t>
-  </si>
-  <si>
-    <t>ounted cash flow model: valuation method</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Cas Flow (FCF): The actual cash the business produces after running costs, tax, and investment (capex). Number a DCF discounts </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue = Total sales </t>
-  </si>
-  <si>
-    <t xml:space="preserve">EBIT = Earning Before Interest and Tax. Profit form core operations, before financing and tax </t>
-  </si>
-  <si>
-    <t xml:space="preserve">EBITDA = Earnings before Interest, Tax, Depreciation and Amortisation. EBIT with non cash D&amp;A added back. A cash earnings measure </t>
-  </si>
-  <si>
-    <t>Underlying vs Statutory: 'Underlying' shows ongoing run rate. 'Statutory' figure straight from the accounting rules</t>
-  </si>
-  <si>
-    <t>D&amp;A (Depreciation &amp; Amortisation) = accounting charge for assets wearing out (depreciation = physical assets; amortisation = intangibles)</t>
-  </si>
-  <si>
-    <t>Capex (Capital Expenditure) = Cash spent buying/building long term assets. A real cash outflow so sibtracted in FCF</t>
-  </si>
-  <si>
-    <t>NOPAT = Net Operating Profit After Tax = EBIT - tax. 'Unlevered' after tax operating profit (ignores debt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WACC = Weighted Average Cost of Capital. The discount rate - the blended return investors (equity + debt) require. Higher WACC ---&gt; lower valuation </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPM = Capital Asset Pricing Model. Formula for cost of equity: risk free rate + beta x equity risk premium </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Risk free rate = the return on a zero risk asset - prexied by the UK 10 year government bond (gilt) yield </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminal growth rate = The asumed prepetual growth beyond the forecast. </t>
-  </si>
-  <si>
-    <t>Terminal value = The value of ALL cash flows beyond the explicit forecast</t>
+    <t xml:space="preserve">DCF (Discounted Cash Flow) - A valuation method: a company is worth the cash it will generate in future, converted to today's value ('discounted') because money later is worth less than money now </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Cash Flow (FCF) - The actual cash the business produces after running costs, tax and investment (Capex). Number the DCF discounts </t>
+  </si>
+  <si>
+    <t>Revenue - Total sales</t>
+  </si>
+  <si>
+    <t>Operating Profit / EBIT - Earnings Before Interest and Tax. Profit from core operations, before financing and tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA - Earnings Before Interest and Tax, Depreciation and Ammortisation. EBIT with non cash D&amp;A added back. </t>
+  </si>
+  <si>
+    <t>D&amp;A (Depreciation &amp; Amortisation) - The accounting charge for assets wearing out. Non cash so it is added back when building FCF</t>
+  </si>
+  <si>
+    <t>Capex (Capital Expenditrure) - Cash spent buying/building long term assets. A real cash outflow, so subtracted in FCF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WACC - Weighted Average Cost of Capital. The discounted rate - Higher WACC ---&gt; Lower valuation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensitivity analysis - A grid showing how value per share changed as WACC and terminal growth vary. Shows the answer is a range, not a single number </t>
   </si>
 </sst>
 </file>
@@ -442,9 +370,9 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="173" formatCode="0.000"/>
-    <numFmt numFmtId="192" formatCode="\£#,##0.00"/>
-    <numFmt numFmtId="193" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="\£#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
@@ -850,7 +778,7 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -902,13 +830,10 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -917,51 +842,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -970,7 +850,7 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -979,16 +859,16 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -997,7 +877,7 @@
     <xf numFmtId="4" fontId="2" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1021,34 +901,82 @@
     <xf numFmtId="10" fontId="15" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="192" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="192" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="192" fontId="2" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="15" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="192" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="192" fontId="0" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="193" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1564,164 +1492,164 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="47" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="48" t="s">
         <v>74</v>
       </c>
       <c r="B2" s="13"/>
-      <c r="C2" s="65">
+      <c r="C2" s="49">
         <v>0.01</v>
       </c>
-      <c r="D2" s="65">
+      <c r="D2" s="49">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="E2" s="65">
+      <c r="E2" s="49">
         <v>0.02</v>
       </c>
-      <c r="F2" s="65">
+      <c r="F2" s="49">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G2" s="66">
+      <c r="G2" s="50">
         <v>0.03</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68">
+      <c r="A3" s="51"/>
+      <c r="B3" s="52">
         <v>8.6900000000000005E-2</v>
       </c>
-      <c r="C3" s="69" cm="1">
+      <c r="C3" s="53" cm="1">
         <f t="array" ref="C3">(SUMPRODUCT($B$11:$F$11/(1+$B3)^$B$12:$F$12)+$F$11*(1+C$2)/($B3-C$2)/(1+$B3)^5-$B$13)/$B$14</f>
         <v>10.218890741952048</v>
       </c>
-      <c r="D3" s="69" cm="1">
+      <c r="D3" s="53" cm="1">
         <f t="array" ref="D3">(SUMPRODUCT($B$11:$F$11/(1+$B3)^$B$12:$F$12)+$F$11*(1+D$2)/($B3-D$2)/(1+$B3)^5-$B$13)/$B$14</f>
         <v>10.704854380845124</v>
       </c>
-      <c r="E3" s="69" cm="1">
+      <c r="E3" s="53" cm="1">
         <f t="array" ref="E3">(SUMPRODUCT($B$11:$F$11/(1+$B3)^$B$12:$F$12)+$F$11*(1+E$2)/($B3-E$2)/(1+$B3)^5-$B$13)/$B$14</f>
         <v>11.263458324505477</v>
       </c>
-      <c r="F3" s="69" cm="1">
+      <c r="F3" s="53" cm="1">
         <f t="array" ref="F3">(SUMPRODUCT($B$11:$F$11/(1+$B3)^$B$12:$F$12)+$F$11*(1+F$2)/($B3-F$2)/(1+$B3)^5-$B$13)/$B$14</f>
         <v>11.91230523160046</v>
       </c>
-      <c r="G3" s="70" cm="1">
+      <c r="G3" s="54" cm="1">
         <f t="array" ref="G3">(SUMPRODUCT($B$11:$F$11/(1+$B3)^$B$12:$F$12)+$F$11*(1+G$2)/($B3-G$2)/(1+$B3)^5-$B$13)/$B$14</f>
         <v>12.675184987042538</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68">
+      <c r="A4" s="51"/>
+      <c r="B4" s="52">
         <v>9.69E-2</v>
       </c>
-      <c r="C4" s="69" cm="1">
+      <c r="C4" s="53" cm="1">
         <f t="array" ref="C4">(SUMPRODUCT($B$11:$F$11/(1+$B4)^$B$12:$F$12)+$F$11*(1+C$2)/($B4-C$2)/(1+$B4)^5-$B$13)/$B$14</f>
         <v>9.1470465715090068</v>
       </c>
-      <c r="D4" s="69" cm="1">
+      <c r="D4" s="53" cm="1">
         <f t="array" ref="D4">(SUMPRODUCT($B$11:$F$11/(1+$B4)^$B$12:$F$12)+$F$11*(1+D$2)/($B4-D$2)/(1+$B4)^5-$B$13)/$B$14</f>
         <v>9.5109997666984931</v>
       </c>
-      <c r="E4" s="69" cm="1">
+      <c r="E4" s="53" cm="1">
         <f t="array" ref="E4">(SUMPRODUCT($B$11:$F$11/(1+$B4)^$B$12:$F$12)+$F$11*(1+E$2)/($B4-E$2)/(1+$B4)^5-$B$13)/$B$14</f>
         <v>9.922281075696759</v>
       </c>
-      <c r="F4" s="69" cm="1">
+      <c r="F4" s="53" cm="1">
         <f t="array" ref="F4">(SUMPRODUCT($B$11:$F$11/(1+$B4)^$B$12:$F$12)+$F$11*(1+F$2)/($B4-F$2)/(1+$B4)^5-$B$13)/$B$14</f>
         <v>10.390764235737898</v>
       </c>
-      <c r="G4" s="70" cm="1">
+      <c r="G4" s="54" cm="1">
         <f t="array" ref="G4">(SUMPRODUCT($B$11:$F$11/(1+$B4)^$B$12:$F$12)+$F$11*(1+G$2)/($B4-G$2)/(1+$B4)^5-$B$13)/$B$14</f>
         <v>10.929274773961565</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="67"/>
-      <c r="B5" s="68">
+      <c r="A5" s="51"/>
+      <c r="B5" s="52">
         <f>'DCF model '!B9</f>
         <v>0.1069</v>
       </c>
-      <c r="C5" s="69" cm="1">
+      <c r="C5" s="53" cm="1">
         <f t="array" ref="C5">(SUMPRODUCT($B$11:$F$11/(1+$B5)^$B$12:$F$12)+$F$11*(1+C$2)/($B5-C$2)/(1+$B5)^5-$B$13)/$B$14</f>
         <v>8.2975951515940523</v>
       </c>
-      <c r="D5" s="69" cm="1">
+      <c r="D5" s="53" cm="1">
         <f t="array" ref="D5">(SUMPRODUCT($B$11:$F$11/(1+$B5)^$B$12:$F$12)+$F$11*(1+D$2)/($B5-D$2)/(1+$B5)^5-$B$13)/$B$14</f>
         <v>8.5781026805217824</v>
       </c>
-      <c r="E5" s="71" cm="1">
+      <c r="E5" s="55" cm="1">
         <f t="array" ref="E5">(SUMPRODUCT($B$11:$F$11/(1+$B5)^$B$12:$F$12)+$F$11*(1+E$2)/($B5-E$2)/(1+$B5)^5-$B$13)/$B$14</f>
         <v>8.890889556852013</v>
       </c>
-      <c r="F5" s="69" cm="1">
+      <c r="F5" s="53" cm="1">
         <f t="array" ref="F5">(SUMPRODUCT($B$11:$F$11/(1+$B5)^$B$12:$F$12)+$F$11*(1+F$2)/($B5-F$2)/(1+$B5)^5-$B$13)/$B$14</f>
         <v>9.241867748973478</v>
       </c>
-      <c r="G5" s="70" cm="1">
+      <c r="G5" s="54" cm="1">
         <f t="array" ref="G5">(SUMPRODUCT($B$11:$F$11/(1+$B5)^$B$12:$F$12)+$F$11*(1+G$2)/($B5-G$2)/(1+$B5)^5-$B$13)/$B$14</f>
         <v>9.6384867983279072</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="67"/>
-      <c r="B6" s="68">
+      <c r="A6" s="51"/>
+      <c r="B6" s="52">
         <v>0.1169</v>
       </c>
-      <c r="C6" s="69" cm="1">
+      <c r="C6" s="53" cm="1">
         <f t="array" ref="C6">(SUMPRODUCT($B$11:$F$11/(1+$B6)^$B$12:$F$12)+$F$11*(1+C$2)/($B6-C$2)/(1+$B6)^5-$B$13)/$B$14</f>
         <v>7.608076015306124</v>
       </c>
-      <c r="D6" s="69" cm="1">
+      <c r="D6" s="53" cm="1">
         <f t="array" ref="D6">(SUMPRODUCT($B$11:$F$11/(1+$B6)^$B$12:$F$12)+$F$11*(1+D$2)/($B6-D$2)/(1+$B6)^5-$B$13)/$B$14</f>
         <v>7.8292878244783024</v>
       </c>
-      <c r="E6" s="69" cm="1">
+      <c r="E6" s="53" cm="1">
         <f t="array" ref="E6">(SUMPRODUCT($B$11:$F$11/(1+$B6)^$B$12:$F$12)+$F$11*(1+E$2)/($B6-E$2)/(1+$B6)^5-$B$13)/$B$14</f>
         <v>8.073328509726041</v>
       </c>
-      <c r="F6" s="69" cm="1">
+      <c r="F6" s="53" cm="1">
         <f t="array" ref="F6">(SUMPRODUCT($B$11:$F$11/(1+$B6)^$B$12:$F$12)+$F$11*(1+F$2)/($B6-F$2)/(1+$B6)^5-$B$13)/$B$14</f>
         <v>8.3439242205720081</v>
       </c>
-      <c r="G6" s="70" cm="1">
+      <c r="G6" s="54" cm="1">
         <f t="array" ref="G6">(SUMPRODUCT($B$11:$F$11/(1+$B6)^$B$12:$F$12)+$F$11*(1+G$2)/($B6-G$2)/(1+$B6)^5-$B$13)/$B$14</f>
         <v>8.6456586783507721</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="72"/>
-      <c r="B7" s="73">
+      <c r="A7" s="56"/>
+      <c r="B7" s="57">
         <v>0.12690000000000001</v>
       </c>
-      <c r="C7" s="74" cm="1">
+      <c r="C7" s="58" cm="1">
         <f t="array" ref="C7">(SUMPRODUCT($B$11:$F$11/(1+$B7)^$B$12:$F$12)+$F$11*(1+C$2)/($B7-C$2)/(1+$B7)^5-$B$13)/$B$14</f>
         <v>7.0374034816464759</v>
       </c>
-      <c r="D7" s="74" cm="1">
+      <c r="D7" s="58" cm="1">
         <f t="array" ref="D7">(SUMPRODUCT($B$11:$F$11/(1+$B7)^$B$12:$F$12)+$F$11*(1+D$2)/($B7-D$2)/(1+$B7)^5-$B$13)/$B$14</f>
         <v>7.2151623379429992</v>
       </c>
-      <c r="E7" s="74" cm="1">
+      <c r="E7" s="58" cm="1">
         <f t="array" ref="E7">(SUMPRODUCT($B$11:$F$11/(1+$B7)^$B$12:$F$12)+$F$11*(1+E$2)/($B7-E$2)/(1+$B7)^5-$B$13)/$B$14</f>
         <v>7.4095497121344263</v>
       </c>
-      <c r="F7" s="74" cm="1">
+      <c r="F7" s="58" cm="1">
         <f t="array" ref="F7">(SUMPRODUCT($B$11:$F$11/(1+$B7)^$B$12:$F$12)+$F$11*(1+F$2)/($B7-F$2)/(1+$B7)^5-$B$13)/$B$14</f>
         <v>7.6230133742739818</v>
       </c>
-      <c r="G7" s="75" cm="1">
+      <c r="G7" s="59" cm="1">
         <f t="array" ref="G7">(SUMPRODUCT($B$11:$F$11/(1+$B7)^$B$12:$F$12)+$F$11*(1+G$2)/($B7-G$2)/(1+$B7)^5-$B$13)/$B$14</f>
         <v>7.8585063101121504</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="76" t="s">
+      <c r="A10" s="60" t="s">
         <v>75</v>
       </c>
       <c r="B10" s="10"/>
@@ -1731,32 +1659,32 @@
       <c r="F10" s="10"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="77" t="s">
+      <c r="A11" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="78">
+      <c r="B11" s="62">
         <f>'DCF model '!B23</f>
         <v>56.558735999999989</v>
       </c>
-      <c r="C11" s="78">
+      <c r="C11" s="62">
         <f>'DCF model '!C23</f>
         <v>61.083434879999999</v>
       </c>
-      <c r="D11" s="78">
+      <c r="D11" s="62">
         <f>'DCF model '!D23</f>
         <v>65.970109670400035</v>
       </c>
-      <c r="E11" s="78">
+      <c r="E11" s="62">
         <f>'DCF model '!E23</f>
         <v>71.247718444032088</v>
       </c>
-      <c r="F11" s="78">
+      <c r="F11" s="62">
         <f>'DCF model '!F23</f>
         <v>76.947535919554653</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="61" t="s">
         <v>77</v>
       </c>
       <c r="B12" s="11">
@@ -1776,30 +1704,30 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="77" t="s">
+      <c r="A13" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="78">
+      <c r="B13" s="62">
         <f>Historicals!D10</f>
         <v>-125.3</v>
       </c>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="79"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="77" t="s">
+      <c r="A14" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="78">
+      <c r="B14" s="62">
         <f>Historicals!D11</f>
         <v>102.6</v>
       </c>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="79"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1832,208 +1760,208 @@
       <c r="B2" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="F2" s="38" t="s">
+      <c r="D2" s="80"/>
+      <c r="F2" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="33"/>
+      <c r="G2" s="71"/>
       <c r="H2" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="33" t="s">
+      <c r="I2" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="28"/>
+      <c r="J2" s="72"/>
     </row>
     <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="28" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="18">
         <v>0.08</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="36"/>
-      <c r="F3" s="39" t="s">
+      <c r="D3" s="77"/>
+      <c r="F3" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="40"/>
+      <c r="G3" s="74"/>
       <c r="H3" s="16">
         <v>4.9399999999999999E-2</v>
       </c>
-      <c r="I3" s="34" t="s">
+      <c r="I3" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="41"/>
+      <c r="J3" s="76"/>
     </row>
     <row r="4" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="18">
         <v>9.8000000000000004E-2</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="F4" s="39" t="s">
+      <c r="D4" s="77"/>
+      <c r="F4" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="40"/>
+      <c r="G4" s="74"/>
       <c r="H4" s="17">
         <v>1.1499999999999999</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="I4" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="41"/>
+      <c r="J4" s="76"/>
     </row>
     <row r="5" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="28" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="18">
         <v>0.25</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="36"/>
-      <c r="F5" s="39" t="s">
+      <c r="D5" s="77"/>
+      <c r="F5" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="40"/>
+      <c r="G5" s="74"/>
       <c r="H5" s="18">
         <v>0.05</v>
       </c>
-      <c r="I5" s="34" t="s">
+      <c r="I5" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="41"/>
+      <c r="J5" s="76"/>
     </row>
     <row r="6" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="28" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="18">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="36"/>
-      <c r="F6" s="42" t="s">
+      <c r="D6" s="77"/>
+      <c r="F6" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="43"/>
+      <c r="G6" s="79"/>
       <c r="H6" s="19">
         <f>H3+H4*H5</f>
         <v>0.1069</v>
       </c>
-      <c r="I6" s="34" t="s">
+      <c r="I6" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="41"/>
+      <c r="J6" s="76"/>
     </row>
     <row r="7" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="28" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="18">
         <v>0.115</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="36"/>
-      <c r="F7" s="39" t="s">
+      <c r="D7" s="77"/>
+      <c r="F7" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="40"/>
+      <c r="G7" s="74"/>
       <c r="H7" s="18">
         <v>0.03</v>
       </c>
-      <c r="I7" s="34" t="s">
+      <c r="I7" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="J7" s="41"/>
+      <c r="J7" s="76"/>
     </row>
     <row r="8" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="28" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="16">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="36"/>
-      <c r="F8" s="39" t="s">
+      <c r="D8" s="77"/>
+      <c r="F8" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="40"/>
+      <c r="G8" s="74"/>
       <c r="H8" s="20">
         <v>1</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="I8" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="41"/>
+      <c r="J8" s="76"/>
     </row>
     <row r="9" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="29" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="22">
         <f>H10</f>
         <v>0.1069</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="36"/>
-      <c r="F9" s="39" t="s">
+      <c r="D9" s="77"/>
+      <c r="F9" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="40"/>
+      <c r="G9" s="74"/>
       <c r="H9" s="20">
         <v>0</v>
       </c>
-      <c r="I9" s="34" t="s">
+      <c r="I9" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="J9" s="41"/>
+      <c r="J9" s="76"/>
     </row>
     <row r="10" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="30" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="23">
         <v>0.02</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="37"/>
-      <c r="F10" s="44" t="s">
+      <c r="D10" s="69"/>
+      <c r="F10" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="45"/>
+      <c r="G10" s="66"/>
       <c r="H10" s="21">
         <f>H8*H6+H9*H7</f>
         <v>0.1069</v>
       </c>
-      <c r="I10" s="35" t="s">
+      <c r="I10" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="J10" s="46"/>
+      <c r="J10" s="68"/>
     </row>
     <row r="13" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
@@ -2047,294 +1975,294 @@
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="47"/>
-      <c r="B14" s="48" t="s">
+      <c r="A14" s="31"/>
+      <c r="B14" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="48" t="s">
+      <c r="D14" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="48" t="s">
+      <c r="E14" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="49" t="s">
+      <c r="F14" s="33" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="56">
+      <c r="B15" s="40">
         <f>Historicals!D5*(1+'DCF model '!$B$3)</f>
         <v>2175.3360000000002</v>
       </c>
-      <c r="C15" s="56">
+      <c r="C15" s="40">
         <f>B15*(1+$B$3)</f>
         <v>2349.3628800000006</v>
       </c>
-      <c r="D15" s="56">
+      <c r="D15" s="40">
         <f t="shared" ref="D15:F15" si="0">C15*(1+$B$3)</f>
         <v>2537.3119104000007</v>
       </c>
-      <c r="E15" s="56">
+      <c r="E15" s="40">
         <f t="shared" si="0"/>
         <v>2740.2968632320008</v>
       </c>
-      <c r="F15" s="56">
+      <c r="F15" s="40">
         <f t="shared" si="0"/>
         <v>2959.5206122905611</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="50" t="s">
+      <c r="A16" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="56">
+      <c r="B16" s="40">
         <f>B17+(B15*$B$6)</f>
         <v>365.45644800000002</v>
       </c>
-      <c r="C16" s="56">
+      <c r="C16" s="40">
         <f t="shared" ref="C16:F16" si="1">C17+(C15*$B$6)</f>
         <v>394.69296384000012</v>
       </c>
-      <c r="D16" s="56">
+      <c r="D16" s="40">
         <f t="shared" si="1"/>
         <v>426.26840094720012</v>
       </c>
-      <c r="E16" s="56">
+      <c r="E16" s="40">
         <f t="shared" si="1"/>
         <v>460.36987302297621</v>
       </c>
-      <c r="F16" s="56">
+      <c r="F16" s="40">
         <f t="shared" si="1"/>
         <v>497.19946286481434</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="50" t="s">
+      <c r="A17" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="57">
+      <c r="B17" s="41">
         <f>B15*$B$4</f>
         <v>213.18292800000003</v>
       </c>
-      <c r="C17" s="57">
+      <c r="C17" s="41">
         <f t="shared" ref="C17:F17" si="2">C15*$B$4</f>
         <v>230.23756224000007</v>
       </c>
-      <c r="D17" s="57">
+      <c r="D17" s="41">
         <f t="shared" si="2"/>
         <v>248.65656721920007</v>
       </c>
-      <c r="E17" s="57">
+      <c r="E17" s="41">
         <f t="shared" si="2"/>
         <v>268.5490925967361</v>
       </c>
-      <c r="F17" s="57">
+      <c r="F17" s="41">
         <f t="shared" si="2"/>
         <v>290.03302000447502</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="50" t="s">
+      <c r="A18" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="56">
+      <c r="B18" s="40">
         <f>-B17*$B$5</f>
         <v>-53.295732000000008</v>
       </c>
-      <c r="C18" s="56">
+      <c r="C18" s="40">
         <f t="shared" ref="C18:F18" si="3">-C17*$B$5</f>
         <v>-57.559390560000018</v>
       </c>
-      <c r="D18" s="56">
+      <c r="D18" s="40">
         <f t="shared" si="3"/>
         <v>-62.164141804800018</v>
       </c>
-      <c r="E18" s="56">
+      <c r="E18" s="40">
         <f t="shared" si="3"/>
         <v>-67.137273149184026</v>
       </c>
-      <c r="F18" s="56">
+      <c r="F18" s="40">
         <f t="shared" si="3"/>
         <v>-72.508255001118755</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="51" t="s">
+      <c r="A19" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="58">
+      <c r="B19" s="42">
         <f>B17+B18</f>
         <v>159.88719600000002</v>
       </c>
-      <c r="C19" s="58">
+      <c r="C19" s="42">
         <f t="shared" ref="C19:F19" si="4">C17+C18</f>
         <v>172.67817168000005</v>
       </c>
-      <c r="D19" s="58">
+      <c r="D19" s="42">
         <f t="shared" si="4"/>
         <v>186.49242541440006</v>
       </c>
-      <c r="E19" s="58">
+      <c r="E19" s="42">
         <f t="shared" si="4"/>
         <v>201.41181944755209</v>
       </c>
-      <c r="F19" s="58">
+      <c r="F19" s="42">
         <f t="shared" si="4"/>
         <v>217.52476500335626</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="59">
+      <c r="B20" s="43">
         <f>B15*$B$6</f>
         <v>152.27352000000002</v>
       </c>
-      <c r="C20" s="59">
+      <c r="C20" s="43">
         <f t="shared" ref="C20:F20" si="5">C15*$B$6</f>
         <v>164.45540160000004</v>
       </c>
-      <c r="D20" s="59">
+      <c r="D20" s="43">
         <f t="shared" si="5"/>
         <v>177.61183372800005</v>
       </c>
-      <c r="E20" s="59">
+      <c r="E20" s="43">
         <f t="shared" si="5"/>
         <v>191.82078042624008</v>
       </c>
-      <c r="F20" s="59">
+      <c r="F20" s="43">
         <f t="shared" si="5"/>
         <v>207.16644286033929</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="50" t="s">
+      <c r="A21" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="56">
+      <c r="B21" s="40">
         <f>-B15*$B$7</f>
         <v>-250.16364000000004</v>
       </c>
-      <c r="C21" s="56">
+      <c r="C21" s="40">
         <f t="shared" ref="C21:F21" si="6">-C15*$B$7</f>
         <v>-270.17673120000006</v>
       </c>
-      <c r="D21" s="56">
+      <c r="D21" s="40">
         <f t="shared" si="6"/>
         <v>-291.79086969600007</v>
       </c>
-      <c r="E21" s="56">
+      <c r="E21" s="40">
         <f t="shared" si="6"/>
         <v>-315.13413927168011</v>
       </c>
-      <c r="F21" s="56">
+      <c r="F21" s="40">
         <f t="shared" si="6"/>
         <v>-340.34487041341453</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="50" t="s">
+      <c r="A22" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="56">
+      <c r="B22" s="40">
         <f>-B15*$B$8</f>
         <v>-5.4383400000000011</v>
       </c>
-      <c r="C22" s="56">
+      <c r="C22" s="40">
         <f t="shared" ref="C22:F22" si="7">-C15*$B$8</f>
         <v>-5.8734072000000017</v>
       </c>
-      <c r="D22" s="56">
+      <c r="D22" s="40">
         <f t="shared" si="7"/>
         <v>-6.3432797760000019</v>
       </c>
-      <c r="E22" s="56">
+      <c r="E22" s="40">
         <f t="shared" si="7"/>
         <v>-6.8507421580800019</v>
       </c>
-      <c r="F22" s="56">
+      <c r="F22" s="40">
         <f t="shared" si="7"/>
         <v>-7.398801530726403</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="52" t="s">
+      <c r="A23" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="B23" s="60">
+      <c r="B23" s="44">
         <f>B19+B20+B21+B22</f>
         <v>56.558735999999989</v>
       </c>
-      <c r="C23" s="60">
+      <c r="C23" s="44">
         <f t="shared" ref="C23:F23" si="8">C19+C20+C21+C22</f>
         <v>61.083434879999999</v>
       </c>
-      <c r="D23" s="60">
+      <c r="D23" s="44">
         <f t="shared" si="8"/>
         <v>65.970109670400035</v>
       </c>
-      <c r="E23" s="60">
+      <c r="E23" s="44">
         <f t="shared" si="8"/>
         <v>71.247718444032088</v>
       </c>
-      <c r="F23" s="60">
+      <c r="F23" s="44">
         <f t="shared" si="8"/>
         <v>76.947535919554653</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="50" t="s">
+      <c r="A24" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="53">
+      <c r="B24" s="37">
         <f>1/(1+$B$9)^1</f>
         <v>0.90342397687234621</v>
       </c>
-      <c r="C24" s="53">
+      <c r="C24" s="37">
         <f>1/(1+$B$9)^2</f>
         <v>0.8161748819878456</v>
       </c>
-      <c r="D24" s="53">
+      <c r="D24" s="37">
         <f>1/(1+$B$9)^3</f>
         <v>0.73735195770877726</v>
       </c>
-      <c r="E24" s="53">
+      <c r="E24" s="37">
         <f>1/(1+$B$9)^4</f>
         <v>0.66614143798787362</v>
       </c>
-      <c r="F24" s="54">
+      <c r="F24" s="38">
         <f>1/(1+$B$9)^5</f>
         <v>0.60180814706646824</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="55" t="s">
+      <c r="A25" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="61">
+      <c r="B25" s="45">
         <f>B23*B24</f>
         <v>51.096518203993128</v>
       </c>
-      <c r="C25" s="61">
+      <c r="C25" s="45">
         <f t="shared" ref="C25:F25" si="9">C23*C24</f>
         <v>49.854765254596252</v>
       </c>
-      <c r="D25" s="61">
+      <c r="D25" s="45">
         <f t="shared" si="9"/>
         <v>48.643189515732203</v>
       </c>
-      <c r="E25" s="61">
+      <c r="E25" s="45">
         <f t="shared" si="9"/>
         <v>47.461057617662682</v>
       </c>
-      <c r="F25" s="61">
+      <c r="F25" s="45">
         <f t="shared" si="9"/>
         <v>46.307654013077695</v>
       </c>
@@ -2370,7 +2298,7 @@
       <c r="A30" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="62">
+      <c r="B30" s="46">
         <f>B27+B29</f>
         <v>786.90526853301651</v>
       </c>
@@ -2413,6 +2341,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="I7:J7"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="C10:D10"/>
@@ -2429,17 +2368,6 @@
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="I9:J9"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2448,7 +2376,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB7A508-F850-44BC-A6CB-EF9B2717D79E}">
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.5">
@@ -2503,169 +2431,59 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="80" t="s">
-        <v>102</v>
-      </c>
-      <c r="G26" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="80" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>108</v>
-      </c>
-      <c r="B35" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>122</v>
-      </c>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" s="64"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" s="64"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
